--- a/education_forms/039_global_education_exchange_registration_form--education_forms.xlsx
+++ b/education_forms/039_global_education_exchange_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'parent/guardian'}</t>
+          <t>parent/guardian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Parent/Guardian'}</t>
+          <t>Parent/Guardian</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'fax'}</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Fax'}</t>
+          <t>Fax</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'arts'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Arts'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'languages'}</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Languages'}</t>
+          <t>Languages</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'europe'}</t>
+          <t>europe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Europe'}</t>
+          <t>Europe</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'asia'}</t>
+          <t>asia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Asia'}</t>
+          <t>Asia</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'africa'}</t>
+          <t>africa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Africa'}</t>
+          <t>Africa</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'short-term'}</t>
+          <t>short-term</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Short-Term'}</t>
+          <t>Short-Term</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'long-term'}</t>
+          <t>long-term</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Long-Term'}</t>
+          <t>Long-Term</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'expiration_of_exchange'}</t>
+          <t>expiration_of_exchange</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Expiration of Exchange'}</t>
+          <t>Expiration of Exchange</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_"participant's_request"}</t>
+          <t>participant's_request</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': "Participant's request"}</t>
+          <t>Participant's request</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
